--- a/260817.xlsx
+++ b/260817.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4C2D075-1F74-4193-B796-B7C92F2F5DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993E77DB-1D08-41F0-94AC-F8A523C97981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="3240" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="4110" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -29,14 +29,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>StichwortIndustrie 4.0 , also die Vernetzung der gesamten Wertschöpfungskette.
-Vor rund 100 Jahren hat Ford eines der ersten permanenten Fließbänder in der Produktion eingeführt.
-Betrachten Sie sich auch in Sachen Industrie 4.0 als Vorreiter, sozusagen aus der historischen Tradition heraus?
-Mattes: ist auch eine Notwendigkeit insbesondere, wenn sie im Volumensegment sind, da haben die Kosten natürlich einen hohen Stellenwert, beziehungsweise.
-Das heißt, wir sind nicht nur, was die Fertigung angeht, in der Planung vollkommen virtuell . welche Gewichte dort verarbeitet werden müssen, wie das alles abläuft, das wird alles virtuell.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Küpper: Wie kann man dem Herr werden – ich habe jetzt kürzlich gehört, dass Ihre Stadt erneut , denn auch Köln ist ja eine hoch verschuldete Stadt?
 Das heißt, Sie haben ja auch ein Interesse daran, den Haushalt irgendwann wieder auszugleichen.
 Reker:  Kostenübernahme durch Bund und Land.
@@ -49,6 +41,9 @@
 In NRW beginnen die ersten Städte, Flüchtlinge zurückzuschicken, zur Rückreise aufzufordern an den Punkt, wo sie sozusagen zugeordnet werden.
 Wird Köln dies auch tun?</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>angeht, in der Planung vollkommen</t>
   </si>
 </sst>
 </file>
@@ -382,9 +377,9 @@
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="308" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -403,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
